--- a/Data/g13.4.xlsx
+++ b/Data/g13.4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,7 +973,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>84.53</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>85.23</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>85.38</v>
+        <v>93.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>86.23</v>
+        <v>94.62</v>
       </c>
     </row>
     <row r="32">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>84.18000000000001</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="33">
@@ -1083,10 +1083,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>01/04/2019</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>85.23</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1101,10 +1103,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>01/07/2019</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>85.38</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1119,10 +1123,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>01/10/2019</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>86.23</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1137,10 +1143,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>84.18000000000001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1155,7 +1163,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1173,7 +1181,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1191,7 +1199,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1209,7 +1217,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1227,12 +1235,10 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>87.28</v>
-      </c>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1247,12 +1253,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>88.04000000000001</v>
-      </c>
+          <t>01/07/2021</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1267,12 +1271,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>89.11</v>
-      </c>
+          <t>01/10/2021</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1287,12 +1289,10 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>87.75</v>
-      </c>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>88.66</v>
+        <v>87.28</v>
       </c>
     </row>
     <row r="46">
@@ -1327,11 +1327,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>89.15000000000001</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1347,11 +1347,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>89.53</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="48">
@@ -1367,11 +1367,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>88.86</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="49">
@@ -1387,11 +1387,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>90.56999999999999</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="50">
@@ -1407,11 +1407,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>91.31</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>91.34</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="52">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>90.12</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="53">
@@ -1467,17 +1467,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91.77</v>
+        <v>90.56999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>84.38</v>
+        <v>91.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>84.45999999999999</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>85.12</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1547,17 +1547,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>84.88</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>84.09999999999999</v>
+        <v>92.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1587,15 +1587,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>92.87</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1605,15 +1607,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>91.65000000000001</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1623,10 +1627,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>92.40000000000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1641,10 +1647,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>84.38</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1659,10 +1667,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>01/04/2019</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>84.45999999999999</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1677,10 +1687,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>01/07/2019</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>85.12</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1695,10 +1707,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>01/10/2019</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>84.88</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1713,10 +1727,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1731,12 +1747,10 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>87.12</v>
-      </c>
+          <t>01/04/2020</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1751,12 +1765,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>87.86</v>
-      </c>
+          <t>01/07/2020</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1771,12 +1783,10 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>88.05</v>
-      </c>
+          <t>01/10/2020</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1791,12 +1801,10 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>88.09</v>
-      </c>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1811,12 +1819,10 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>89.73</v>
-      </c>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1831,12 +1837,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>90.18000000000001</v>
-      </c>
+          <t>01/07/2021</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1851,12 +1855,10 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>88.73</v>
-      </c>
+          <t>01/10/2021</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1871,12 +1873,10 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>89.89</v>
-      </c>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1891,11 +1891,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>90.77</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="76">
@@ -1911,11 +1911,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>91.56</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="77">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>91.5</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="78">
@@ -1951,11 +1951,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>90.66</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="79">
@@ -1971,11 +1971,251 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>01/04/2023</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>89.73</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>01/07/2023</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>90.18000000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>88.73</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>89.89</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>90.77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>91.56</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>91.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>90.66</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D87" t="n">
         <v>91.95</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>92.26000000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>92.48999999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>91.33</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>92.15000000000001</v>
       </c>
     </row>
   </sheetData>
